--- a/out/toc.xlsx
+++ b/out/toc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69CC12AA-AADD-4814-9FD6-B747CB98A22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2C2367C-4D4F-4672-9389-1C5135602293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="3300" windowWidth="23840" windowHeight="12700" xr2:uid="{1DEBD4C7-D127-4229-BF26-EC7DBDA04433}"/>
+    <workbookView xWindow="1760" yWindow="3040" windowWidth="23840" windowHeight="12700" xr2:uid="{AAC363B7-C50E-49A9-94C3-5A1E61891071}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -182,7 +182,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{A839195C-2B8E-4BFD-B248-8010E5309F0E}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{FF6E7738-5597-4AA9-A87F-E925D23B4B04}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,7 +513,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F9B69B-13E1-4C49-8443-63401D406B3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE81A70-3BA3-44CA-9472-EC431384900B}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
